--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_atacama.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_atacama.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:22</t>
+    <t xml:space="preserve">2026-09-24 01:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -739,7 +739,7 @@
         <v>0.2</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0.08</v>
@@ -759,10 +759,10 @@
         <v>9</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>-0.55</v>
@@ -785,7 +785,7 @@
         <v>0.16</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0.21</v>
@@ -805,10 +805,10 @@
         <v>9</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0.33</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_atacama.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_atacama.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:13</t>
+    <t xml:space="preserve">2026-10-01 23:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_atacama.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_atacama.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:08</t>
+    <t xml:space="preserve">2026-10-05 19:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
